--- a/gte/nodes/LPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_2_blade_stator_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0011194877941022865</v>
       </c>
       <c r="B2">
-        <v>0.00068561494341950612</v>
+        <v>0.00060277284665593688</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.002238975588204573</v>
       </c>
       <c r="B3">
-        <v>0.0011454085283322791</v>
+        <v>0.0010312207733338455</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0033584633823068597</v>
       </c>
       <c r="B4">
-        <v>0.0015569926633398977</v>
+        <v>0.0014186239719888552</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.004477951176409146</v>
       </c>
       <c r="B5">
-        <v>0.001930482246838461</v>
+        <v>0.0017726344678700387</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0055974389705114322</v>
       </c>
       <c r="B6">
-        <v>0.0022701348379030009</v>
+        <v>0.0020965064437916364</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0067169267646137194</v>
       </c>
       <c r="B7">
-        <v>0.0025784597874031266</v>
+        <v>0.0023921770184645061</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0078364145587160056</v>
       </c>
       <c r="B8">
-        <v>0.0028570101276439806</v>
+        <v>0.002660863241104323</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0089559023528182919</v>
       </c>
       <c r="B9">
-        <v>0.0031080748979776572</v>
+        <v>0.0029043281194510414</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.010075390146920578</v>
       </c>
       <c r="B10">
-        <v>0.0033340999668129727</v>
+        <v>0.0031244494479585505</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.011194877941022864</v>
       </c>
       <c r="B11">
-        <v>0.0035374225117386733</v>
+        <v>0.0033230182094122034</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.012314365735125153</v>
       </c>
       <c r="B12">
-        <v>0.0037193495355712855</v>
+        <v>0.003501050212150972</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.013433853529227439</v>
       </c>
       <c r="B13">
-        <v>0.0038771760328585227</v>
+        <v>0.0036565473783968442</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.014553341323329725</v>
       </c>
       <c r="B14">
-        <v>0.0040093226842352276</v>
+        <v>0.0037883534399307038</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.015672829117432011</v>
       </c>
       <c r="B15">
-        <v>0.0041227249229535681</v>
+        <v>0.0039016932528860124</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.016792316911534298</v>
       </c>
       <c r="B16">
-        <v>0.0042237433683961585</v>
+        <v>0.0040013585033696524</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.017911804705636584</v>
       </c>
       <c r="B17">
-        <v>0.0043079246318500769</v>
+        <v>0.00408402707302962</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.01903129249973887</v>
       </c>
       <c r="B18">
-        <v>0.004369487422657789</v>
+        <v>0.0041453783366783769</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B19">
-        <v>0.0044081528504788421</v>
+        <v>0.0041852114462451384</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.021270268087943443</v>
       </c>
       <c r="B20">
-        <v>0.0044250176250520586</v>
+        <v>0.0042043554979383111</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.022389755882045729</v>
       </c>
       <c r="B21">
-        <v>0.0044211784561162563</v>
+        <v>0.0042036395879662992</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.023509243676148015</v>
       </c>
       <c r="B22">
-        <v>0.0043975329943717143</v>
+        <v>0.0041837413737053526</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.024628731470250305</v>
       </c>
       <c r="B23">
-        <v>0.0043541826543645476</v>
+        <v>0.0041447327572030953</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.025748219264352591</v>
       </c>
       <c r="B24">
-        <v>0.0042910297916023271</v>
+        <v>0.0040865342016749981</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.026867707058454877</v>
       </c>
       <c r="B25">
-        <v>0.0042079767615926245</v>
+        <v>0.00400906617033653</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.02798719485255716</v>
       </c>
       <c r="B26">
-        <v>0.00410488615277732</v>
+        <v>0.0039122171817599465</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.02910668264665945</v>
       </c>
       <c r="B27">
-        <v>0.0039814614853355143</v>
+        <v>0.0037957479759446306</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.030226170440761736</v>
       </c>
       <c r="B28">
-        <v>0.0038373665123806171</v>
+        <v>0.0036593873482467522</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.031345658234864023</v>
       </c>
       <c r="B29">
-        <v>0.0036722649870260392</v>
+        <v>0.0035028640940224808</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.032465146028966309</v>
       </c>
       <c r="B30">
-        <v>0.0034859535654180435</v>
+        <v>0.0033260043819165678</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B31">
-        <v>0.0032787605158343179</v>
+        <v>0.003129023873728101</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.034704121617170881</v>
       </c>
       <c r="B32">
-        <v>0.0030511470095854012</v>
+        <v>0.0029122356045447472</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.035823609411273168</v>
       </c>
       <c r="B33">
-        <v>0.0028035742179818358</v>
+        <v>0.0026759526094541752</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.036943097205375454</v>
       </c>
       <c r="B34">
-        <v>0.0025362629808304738</v>
+        <v>0.0024203049238091328</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.03806258499947774</v>
       </c>
       <c r="B35">
-        <v>0.0022484728119234131</v>
+        <v>0.0021446905840226773</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.039182072793580026</v>
       </c>
       <c r="B36">
-        <v>0.0019392228935490644</v>
+        <v>0.0018483246267729447</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B37">
-        <v>0.0016075324079958334</v>
+        <v>0.0015304220887380677</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.0414210483817846</v>
       </c>
       <c r="B38">
-        <v>0.0012518463431808447</v>
+        <v>0.0011897644618725917</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.042540536175886885</v>
       </c>
       <c r="B39">
-        <v>0.00086831290953607936</v>
+        <v>0.00082339905923669568</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.043660023969989178</v>
       </c>
       <c r="B40">
-        <v>0.00045250612312223212</v>
+        <v>0.00042793964916696835</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.043660023969989178</v>
       </c>
       <c r="B43">
-        <v>0.00025597433148012228</v>
+        <v>0.000280540805435386</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.042540536175886885</v>
       </c>
       <c r="B44">
-        <v>0.00050900210714101008</v>
+        <v>0.00055391595744039377</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.0414210483817846</v>
       </c>
       <c r="B45">
-        <v>0.00075519129271482</v>
+        <v>0.000817273174023073</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B46">
-        <v>0.00099064985393370946</v>
+        <v>0.0010677601731914749</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.039182072793580026</v>
       </c>
       <c r="B47">
-        <v>0.0012120367593401074</v>
+        <v>0.0013029350261162269</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.03806258499947774</v>
       </c>
       <c r="B48">
-        <v>0.0014182149887175244</v>
+        <v>0.0015219972166182604</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.036943097205375454</v>
       </c>
       <c r="B49">
-        <v>0.0016085985246597448</v>
+        <v>0.001724556581681086</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.035823609411273168</v>
       </c>
       <c r="B50">
-        <v>0.0017826013497605504</v>
+        <v>0.001910222958288211</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.034704121617170881</v>
       </c>
       <c r="B51">
-        <v>0.0019398557692601654</v>
+        <v>0.00207876717430082</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B52">
-        <v>0.0020808673789845843</v>
+        <v>0.0022306040210908012</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.032465146028966309</v>
       </c>
       <c r="B53">
-        <v>0.002206360097406242</v>
+        <v>0.0023663092809077168</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.031345658234864023</v>
       </c>
       <c r="B54">
-        <v>0.0023170578429975754</v>
+        <v>0.0024864587360011329</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.030226170440761736</v>
       </c>
       <c r="B55">
-        <v>0.0024135331993096992</v>
+        <v>0.0025915123634435641</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.02910668264665945</v>
       </c>
       <c r="B56">
-        <v>0.0024957534102084478</v>
+        <v>0.0026814669195993311</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.02798719485255716</v>
       </c>
       <c r="B57">
-        <v>0.0025635343846383339</v>
+        <v>0.0027562033556557072</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.026867707058454877</v>
       </c>
       <c r="B58">
-        <v>0.0026166920315438707</v>
+        <v>0.0028156026227999652</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.025748219264352591</v>
       </c>
       <c r="B59">
-        <v>0.0026550650721836942</v>
+        <v>0.0028595606621110228</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.024628731470250305</v>
       </c>
       <c r="B60">
-        <v>0.0026785834770729272</v>
+        <v>0.0028880333742343795</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.023509243676148015</v>
       </c>
       <c r="B61">
-        <v>0.0026872000290408156</v>
+        <v>0.0029009916497071777</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.022389755882045729</v>
       </c>
       <c r="B62">
-        <v>0.0026808675109166054</v>
+        <v>0.0028984063790665616</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.021270268087943443</v>
       </c>
       <c r="B63">
-        <v>0.0026597206081420844</v>
+        <v>0.002880382735255831</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B64">
-        <v>0.0026246216166092118</v>
+        <v>0.0028475630208429159</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.01903129249973887</v>
       </c>
       <c r="B65">
-        <v>0.00257661473482249</v>
+        <v>0.0028007238208019023</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.017911804705636584</v>
       </c>
       <c r="B66">
-        <v>0.0025167441612864187</v>
+        <v>0.0027406417201068763</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.016792316911534298</v>
       </c>
       <c r="B67">
-        <v>0.0024446644481841118</v>
+        <v>0.0026670493132106175</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.015672829117432011</v>
       </c>
       <c r="B68">
-        <v>0.0023544715624131247</v>
+        <v>0.00257550323248068</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.014553341323329725</v>
       </c>
       <c r="B69">
-        <v>0.0022415687297990374</v>
+        <v>0.0024625379741035612</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.013433853529227439</v>
       </c>
       <c r="B70">
-        <v>0.0021121467971650931</v>
+        <v>0.002332775451626772</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.012314365735125153</v>
       </c>
       <c r="B71">
-        <v>0.00197295494820878</v>
+        <v>0.002191254271629093</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.011194877941022864</v>
       </c>
       <c r="B72">
-        <v>0.0018221880931269139</v>
+        <v>0.0020365923954533838</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.010075390146920578</v>
       </c>
       <c r="B73">
-        <v>0.0016568958159775946</v>
+        <v>0.0018665463348320167</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0089559023528182919</v>
       </c>
       <c r="B74">
-        <v>0.0014781006697647285</v>
+        <v>0.0016818474482913446</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0078364145587160056</v>
       </c>
       <c r="B75">
-        <v>0.0012878350353267203</v>
+        <v>0.0014839819218663776</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0067169267646137194</v>
       </c>
       <c r="B76">
-        <v>0.0010881976358941628</v>
+        <v>0.0012744804048327835</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0055974389705114322</v>
       </c>
       <c r="B77">
-        <v>0.00088110768501208634</v>
+        <v>0.0010547360791234508</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.004477951176409146</v>
       </c>
       <c r="B78">
-        <v>0.00066770001509108194</v>
+        <v>0.00082554779405950439</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0033584633823068597</v>
       </c>
       <c r="B79">
-        <v>0.00045004313253155692</v>
+        <v>0.00058841182388259957</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.002238975588204573</v>
       </c>
       <c r="B80">
-        <v>0.00023190648834481328</v>
+        <v>0.00034609424334324656</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0011194877941022865</v>
       </c>
       <c r="B81">
-        <v>2.2878169310952516E-05</v>
+        <v>0.00010572026607452176</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0012394846175045778</v>
       </c>
       <c r="B2">
-        <v>0.00095729553128413652</v>
+        <v>0.00086557366958879783</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0024789692350091555</v>
       </c>
       <c r="B3">
-        <v>0.0015495600998720117</v>
+        <v>0.001423132668886545</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0037184538525137337</v>
       </c>
       <c r="B4">
-        <v>0.0020716495991286777</v>
+        <v>0.0019184493004051116</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.004957938470018311</v>
       </c>
       <c r="B5">
-        <v>0.0025402521002660921</v>
+        <v>0.0023654847691979473</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0061974230875228888</v>
       </c>
       <c r="B6">
-        <v>0.0029623355521090837</v>
+        <v>0.002770096096889624</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0074369077050274674</v>
       </c>
       <c r="B7">
-        <v>0.0033419739757975073</v>
+        <v>0.0031357237354447455</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0086763923225320443</v>
       </c>
       <c r="B8">
-        <v>0.0036816577397512976</v>
+        <v>0.0034644860564885254</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.009915876940036622</v>
       </c>
       <c r="B9">
-        <v>0.003985109430492041</v>
+        <v>0.0037595232301062083</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0111553615575412</v>
       </c>
       <c r="B10">
-        <v>0.0042563167638761277</v>
+        <v>0.0040241940068966378</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.012394846175045778</v>
       </c>
       <c r="B11">
-        <v>0.0044990957549975105</v>
+        <v>0.0042617096610530342</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.013634330792550357</v>
       </c>
       <c r="B12">
-        <v>0.0047155557824846619</v>
+        <v>0.0044738571638694305</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.014873815410054935</v>
       </c>
       <c r="B13">
-        <v>0.004901151379866543</v>
+        <v>0.0046568737514487406</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.016113300027559511</v>
       </c>
       <c r="B14">
-        <v>0.0050532107731786832</v>
+        <v>0.0048085560474193031</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.017352784645064089</v>
       </c>
       <c r="B15">
-        <v>0.0051832118035824055</v>
+        <v>0.0049384879607023017</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.018592269262568666</v>
       </c>
       <c r="B16">
-        <v>0.0053016812020491143</v>
+        <v>0.0050554591165397119</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.019831753880073244</v>
       </c>
       <c r="B17">
-        <v>0.0054011916436647696</v>
+        <v>0.005153294720163854</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.021071238497577825</v>
       </c>
       <c r="B18">
-        <v>0.0054721149186164114</v>
+        <v>0.0052239837945631615</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.0223107231150824</v>
       </c>
       <c r="B19">
-        <v>0.0055139733333808318</v>
+        <v>0.005267135053760163</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.023550207732586977</v>
       </c>
       <c r="B20">
-        <v>0.0055285768235072653</v>
+        <v>0.0052842621345359107</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.024789692350091555</v>
       </c>
       <c r="B21">
-        <v>0.005517735324544944</v>
+        <v>0.0052768786736714559</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.026029176967596133</v>
       </c>
       <c r="B22">
-        <v>0.0054829319238383486</v>
+        <v>0.0052462241843137525</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.027268661585100714</v>
       </c>
       <c r="B23">
-        <v>0.0054243423159129438</v>
+        <v>0.005192441685073359</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.028508146202605292</v>
       </c>
       <c r="B24">
-        <v>0.005341815347089442</v>
+        <v>0.0051154000709267358</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.02974763082010987</v>
       </c>
       <c r="B25">
-        <v>0.0052351998636885558</v>
+        <v>0.005014968236850343</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.030987115437614444</v>
       </c>
       <c r="B26">
-        <v>0.0051042823491022349</v>
+        <v>0.00489096137579232</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.032226600055119022</v>
       </c>
       <c r="B27">
-        <v>0.0049485998350073659</v>
+        <v>0.0047429798725875166</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.0334660846726236</v>
       </c>
       <c r="B28">
-        <v>0.0047676269901520737</v>
+        <v>0.0045705704100424639</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.034705569290128177</v>
       </c>
       <c r="B29">
-        <v>0.0045608384832844838</v>
+        <v>0.0043732796709636916</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.035945053907632758</v>
       </c>
       <c r="B30">
-        <v>0.0043279336471511035</v>
+        <v>0.0041508396640126139</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.037184538525137333</v>
       </c>
       <c r="B31">
-        <v>0.0040695104704919771</v>
+        <v>0.0039037237012701891</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.038424023142641914</v>
       </c>
       <c r="B32">
-        <v>0.0037863916060455242</v>
+        <v>0.0036325904206722542</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.039663507760146488</v>
       </c>
       <c r="B33">
-        <v>0.0034793997065501736</v>
+        <v>0.0033380984601546516</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.040902992377651069</v>
       </c>
       <c r="B34">
-        <v>0.0031489628544901492</v>
+        <v>0.0030205753645051185</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.04214247699515565</v>
       </c>
       <c r="B35">
-        <v>0.0027939308513328788</v>
+        <v>0.0026790243059189823</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.043381961612660225</v>
       </c>
       <c r="B36">
-        <v>0.0024127589282915913</v>
+        <v>0.0023121173634434683</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.0446214462301648</v>
       </c>
       <c r="B37">
-        <v>0.0020039023165795114</v>
+        <v>0.0019185266161257963</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.04586093084766938</v>
       </c>
       <c r="B38">
-        <v>0.001564867284795996</v>
+        <v>0.0014961309061479106</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.047100415465173955</v>
       </c>
       <c r="B39">
-        <v>0.00108936425108491</v>
+        <v>0.0010396361282306267</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.048339900082678536</v>
       </c>
       <c r="B40">
-        <v>0.00057015467097624626</v>
+        <v>0.00054295494022947761</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.048339900082678536</v>
       </c>
       <c r="B43">
-        <v>0.00024375790201502226</v>
+        <v>0.00027095763276179088</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.047100415465173955</v>
       </c>
       <c r="B44">
-        <v>0.00049262677683350737</v>
+        <v>0.000542354899687791</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.04586093084766938</v>
       </c>
       <c r="B45">
-        <v>0.00074003074101897061</v>
+        <v>0.000808767119667056</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.0446214462301648</v>
       </c>
       <c r="B46">
-        <v>0.00097939391113492777</v>
+        <v>0.0010647696115886431</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.043381961612660225</v>
       </c>
       <c r="B47">
-        <v>0.0012050601501141121</v>
+        <v>0.0013057017149622355</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.04214247699515565</v>
       </c>
       <c r="B48">
-        <v>0.0014150523063661245</v>
+        <v>0.0015299588517800208</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.040902992377651069</v>
       </c>
       <c r="B49">
-        <v>0.0016083129746697848</v>
+        <v>0.0017367004646548152</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.039663507760146488</v>
       </c>
       <c r="B50">
-        <v>0.0017837847498039109</v>
+        <v>0.0019250859961994331</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.038424023142641914</v>
       </c>
       <c r="B51">
-        <v>0.0019407773815662828</v>
+        <v>0.0020945785669395532</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.037184538525137333</v>
       </c>
       <c r="B52">
-        <v>0.0020800692398305256</v>
+        <v>0.0022458560090523132</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.035945053907632758</v>
       </c>
       <c r="B53">
-        <v>0.0022028058494892259</v>
+        <v>0.0023798998326277159</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.034705569290128177</v>
       </c>
       <c r="B54">
-        <v>0.0023101327354349724</v>
+        <v>0.0024976915477557646</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.0334660846726236</v>
       </c>
       <c r="B55">
-        <v>0.002402948028836754</v>
+        <v>0.0026000046089463638</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.032226600055119022</v>
       </c>
       <c r="B56">
-        <v>0.0024811602859691785</v>
+        <v>0.0026867802483890274</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.030987115437614444</v>
       </c>
       <c r="B57">
-        <v>0.0025444306693832557</v>
+        <v>0.0027577516426931705</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.02974763082010987</v>
       </c>
       <c r="B58">
-        <v>0.0025924203416299962</v>
+        <v>0.0028126519684682095</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.028508146202605292</v>
       </c>
       <c r="B59">
-        <v>0.0026248320331369625</v>
+        <v>0.0028512473092996687</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.027268661585100714</v>
       </c>
       <c r="B60">
-        <v>0.0026415347458379188</v>
+        <v>0.002873435376677504</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.026029176967596133</v>
       </c>
       <c r="B61">
-        <v>0.0026424390495431828</v>
+        <v>0.00287914678906778</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.024789692350091555</v>
       </c>
       <c r="B62">
-        <v>0.0026274555140630707</v>
+        <v>0.0028683121649365597</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.023550207732586977</v>
       </c>
       <c r="B63">
-        <v>0.0025968005558510017</v>
+        <v>0.0028411152448223568</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.0223107231150824</v>
       </c>
       <c r="B64">
-        <v>0.0025519139779328084</v>
+        <v>0.0027987522575534762</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.021071238497577825</v>
       </c>
       <c r="B65">
-        <v>0.0024945414299774238</v>
+        <v>0.0027426725540306727</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.019831753880073244</v>
       </c>
       <c r="B66">
-        <v>0.0024264285616537834</v>
+        <v>0.0026743254851546989</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.018592269262568666</v>
       </c>
       <c r="B67">
-        <v>0.002347016175936282</v>
+        <v>0.0025932382614456849</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.017352784645064089</v>
       </c>
       <c r="B68">
-        <v>0.0022465256890211597</v>
+        <v>0.0024912495319012631</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.016113300027559511</v>
       </c>
       <c r="B69">
-        <v>0.0021173540640661227</v>
+        <v>0.0023620087898255028</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.014873815410054935</v>
       </c>
       <c r="B70">
-        <v>0.0019698198388529158</v>
+        <v>0.0022140974672707177</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.013634330792550357</v>
       </c>
       <c r="B71">
-        <v>0.0018151723591018885</v>
+        <v>0.0020568709777171196</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.012394846175045778</v>
       </c>
       <c r="B72">
-        <v>0.0016504626276637902</v>
+        <v>0.0018878487216082665</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0111553615575412</v>
       </c>
       <c r="B73">
-        <v>0.0014708436801222529</v>
+        <v>0.0017029664371017422</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.009915876940036622</v>
       </c>
       <c r="B74">
-        <v>0.0012780750258620432</v>
+        <v>0.0015036612262478764</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0086763923225320443</v>
       </c>
       <c r="B75">
-        <v>0.0010755975405980316</v>
+        <v>0.0012927692238608039</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0074369077050274674</v>
       </c>
       <c r="B76">
-        <v>0.000866971091564366</v>
+        <v>0.0010732213319171278</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0061974230875228888</v>
       </c>
       <c r="B77">
-        <v>0.000655462089475565</v>
+        <v>0.00084770154469502473</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.004957938470018311</v>
       </c>
       <c r="B78">
-        <v>0.00044304412744834715</v>
+        <v>0.00061781145851649247</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0037184538525137337</v>
       </c>
       <c r="B79">
-        <v>0.00023324601444588773</v>
+        <v>0.0003864463131694534</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0024789692350091555</v>
       </c>
       <c r="B80">
-        <v>3.2430928046409048E-05</v>
+        <v>0.0001588583590318759</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0012394846175045778</v>
       </c>
       <c r="B81">
-        <v>-0.00014336680905992842</v>
+        <v>-5.1644947364589719E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0013433853529227439</v>
       </c>
       <c r="B2">
-        <v>0.0012416785793838321</v>
+        <v>0.0011422680632675493</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0026867707058454877</v>
       </c>
       <c r="B3">
-        <v>0.0019637817450158775</v>
+        <v>0.0018267564390177572</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0040301560587682316</v>
       </c>
       <c r="B4">
-        <v>0.0025922927702463215</v>
+        <v>0.0024262503406250707</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0053735414116909755</v>
       </c>
       <c r="B5">
-        <v>0.0031512228900782958</v>
+        <v>0.0029618055553161889</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0067169267646137185</v>
       </c>
       <c r="B6">
-        <v>0.0036505444446359413</v>
+        <v>0.0034421903717023038</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0080603121175364632</v>
       </c>
       <c r="B7">
-        <v>0.0040960571234112631</v>
+        <v>0.0038725178006849183</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0094036974704592071</v>
       </c>
       <c r="B8">
-        <v>0.0044912765688716483</v>
+        <v>0.00425590030502406</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.010747082823381951</v>
       </c>
       <c r="B9">
-        <v>0.0048415087019307631</v>
+        <v>0.0045970125676988239</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.012090468176304693</v>
       </c>
       <c r="B10">
-        <v>0.0051524470852913427</v>
+        <v>0.0049008664626660359</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.013433853529227437</v>
       </c>
       <c r="B11">
-        <v>0.0054295455703661406</v>
+        <v>0.0051722604075743759</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.014777238882150183</v>
       </c>
       <c r="B12">
-        <v>0.0056757957905623881</v>
+        <v>0.0054138366024580114</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.016120624235072926</v>
       </c>
       <c r="B13">
-        <v>0.0058845802185552125</v>
+        <v>0.0056198258332011974</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.017464009587995669</v>
       </c>
       <c r="B14">
-        <v>0.0060519929088971147</v>
+        <v>0.0057868298157316856</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.018807394940918414</v>
       </c>
       <c r="B15">
-        <v>0.0061945834043821927</v>
+        <v>0.0059293454003011264</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B16">
-        <v>0.0063275300770127794</v>
+        <v>0.006060668238980973</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.021494165646763902</v>
       </c>
       <c r="B17">
-        <v>0.0064400711273825554</v>
+        <v>0.0061713940567980066</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.022837550999686644</v>
       </c>
       <c r="B18">
-        <v>0.0065182683664274411</v>
+        <v>0.0062493374632521465</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.024180936352609386</v>
       </c>
       <c r="B19">
-        <v>0.0065614182178609709</v>
+        <v>0.0062938885327805264</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.025524321705532132</v>
       </c>
       <c r="B20">
-        <v>0.006572125758591083</v>
+        <v>0.0063073312060545868</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.026867707058454874</v>
       </c>
       <c r="B21">
-        <v>0.0065529960655257152</v>
+        <v>0.0062919494237457683</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.02821109241137762</v>
       </c>
       <c r="B22">
-        <v>0.006506165305343062</v>
+        <v>0.0062496153605434285</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.029554477764300365</v>
       </c>
       <c r="B23">
-        <v>0.0064318940038023496</v>
+        <v>0.0061805541272086069</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.030897863117223107</v>
       </c>
       <c r="B24">
-        <v>0.0063299737764330576</v>
+        <v>0.0060845790685202629</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.032241248470145853</v>
       </c>
       <c r="B25">
-        <v>0.0062001962387646693</v>
+        <v>0.0059615035292573558</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B26">
-        <v>0.0060422662627777207</v>
+        <v>0.0058110634975568724</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.034928019175991337</v>
       </c>
       <c r="B27">
-        <v>0.005855541746256963</v>
+        <v>0.0056326855349879031</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.036271404528914079</v>
       </c>
       <c r="B28">
-        <v>0.0056392938434382048</v>
+        <v>0.0054257188464775672</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.037614789881836828</v>
       </c>
       <c r="B29">
-        <v>0.0053927937085572518</v>
+        <v>0.0051895126369529837</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.038958175234759571</v>
       </c>
       <c r="B30">
-        <v>0.0051156408261126187</v>
+        <v>0.0049237018059108484</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B31">
-        <v>0.0048087480016536389</v>
+        <v>0.0046290640311261793</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.041644945940605055</v>
       </c>
       <c r="B32">
-        <v>0.0044733563709923492</v>
+        <v>0.0043066626849435647</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.042988331293527804</v>
       </c>
       <c r="B33">
-        <v>0.0041107070699407909</v>
+        <v>0.003957561139707598</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.044331716646450546</v>
       </c>
       <c r="B34">
-        <v>0.0037214754124169913</v>
+        <v>0.0035823257439913814</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.045675101999373288</v>
       </c>
       <c r="B35">
-        <v>0.0033040734247629391</v>
+        <v>0.0031795347512820556</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.04701848735229603</v>
       </c>
       <c r="B36">
-        <v>0.0028563473114266141</v>
+        <v>0.002747269391295271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.048361872705218772</v>
       </c>
       <c r="B37">
-        <v>0.0023761432768559894</v>
+        <v>0.0022836108937466714</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.049705258058141522</v>
       </c>
       <c r="B38">
-        <v>0.0018599407752617001</v>
+        <v>0.0017854425176917967</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.051048643411064264</v>
       </c>
       <c r="B39">
-        <v>0.0012987522599049997</v>
+        <v>0.0012448556395457393</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.052392028763987006</v>
       </c>
       <c r="B40">
-        <v>0.00068222343380979563</v>
+        <v>0.000652743665063479</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.052392028763987006</v>
       </c>
       <c r="B43">
-        <v>0.00021054713386873243</v>
+        <v>0.00024002690261504893</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.051048643411064264</v>
       </c>
       <c r="B44">
-        <v>0.00043640633415683352</v>
+        <v>0.000490302954516094</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.049705258058141522</v>
       </c>
       <c r="B45">
-        <v>0.00066796865414324078</v>
+        <v>0.00074246691171314433</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.048361872705218772</v>
       </c>
       <c r="B46">
-        <v>0.00089562514710689236</v>
+        <v>0.0009881575302162107</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.04701848735229603</v>
       </c>
       <c r="B47">
-        <v>0.001111100589325117</v>
+        <v>0.0012201785094564609</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.045675101999373288</v>
       </c>
       <c r="B48">
-        <v>0.0013114546490688057</v>
+        <v>0.0014359933225496892</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.044331716646450546</v>
       </c>
       <c r="B49">
-        <v>0.0014950807176072416</v>
+        <v>0.0016342303860328511</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.042988331293527804</v>
       </c>
       <c r="B50">
-        <v>0.0016603721862097059</v>
+        <v>0.0018135181164428988</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.041644945940605055</v>
       </c>
       <c r="B51">
-        <v>0.0018062573942117842</v>
+        <v>0.0019729510802605696</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.040301560587682313</v>
       </c>
       <c r="B52">
-        <v>0.0019338044732142789</v>
+        <v>0.0021134884437417388</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.038958175234759571</v>
       </c>
       <c r="B53">
-        <v>0.0020446165028842954</v>
+        <v>0.0022365555230860652</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.037614789881836828</v>
       </c>
       <c r="B54">
-        <v>0.00214029656288894</v>
+        <v>0.0023435776344932096</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.036271404528914079</v>
       </c>
       <c r="B55">
-        <v>0.0022220938920680024</v>
+        <v>0.0024356688890286395</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.034928019175991337</v>
       </c>
       <c r="B56">
-        <v>0.0022898423659520051</v>
+        <v>0.0025126985772210646</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.033584633823068595</v>
       </c>
       <c r="B57">
-        <v>0.0023430220192441555</v>
+        <v>0.0025742247844650033</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.032241248470145853</v>
       </c>
       <c r="B58">
-        <v>0.0023811128866476606</v>
+        <v>0.0026198055961549737</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.030897863117223107</v>
       </c>
       <c r="B59">
-        <v>0.0024036584498283394</v>
+        <v>0.0026490531577411341</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.029554477764300365</v>
       </c>
       <c r="B60">
-        <v>0.0024104559783024609</v>
+        <v>0.002661795854896204</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.02821109241137762</v>
       </c>
       <c r="B61">
-        <v>0.0024013661885489059</v>
+        <v>0.0026579161333485403</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.026867707058454874</v>
       </c>
       <c r="B62">
-        <v>0.0023762497970465546</v>
+        <v>0.0026372964388265015</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.025524321705532132</v>
       </c>
       <c r="B63">
-        <v>0.0023354129180071471</v>
+        <v>0.0026002074705436425</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.024180936352609386</v>
       </c>
       <c r="B64">
-        <v>0.0022809432565738586</v>
+        <v>0.0025484729416543027</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.022837550999686644</v>
       </c>
       <c r="B65">
-        <v>0.0022153739156227231</v>
+        <v>0.0024843048187980178</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.021494165646763902</v>
       </c>
       <c r="B66">
-        <v>0.0021412379980297754</v>
+        <v>0.0024099150686143237</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.020150780293841156</v>
       </c>
       <c r="B67">
-        <v>0.0020577406685038675</v>
+        <v>0.0023246025065356748</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.018807394940918414</v>
       </c>
       <c r="B68">
-        <v>0.0019507753390851288</v>
+        <v>0.0022160133431661949</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.017464009587995669</v>
       </c>
       <c r="B69">
-        <v>0.0018093834182502594</v>
+        <v>0.0020745465114156876</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.016120624235072926</v>
       </c>
       <c r="B70">
-        <v>0.0016485100528909828</v>
+        <v>0.0019132644382449972</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.014777238882150183</v>
       </c>
       <c r="B71">
-        <v>0.0014844487808923759</v>
+        <v>0.0017464079689967519</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.013433853529227437</v>
       </c>
       <c r="B72">
-        <v>0.0013129829656979184</v>
+        <v>0.0015702681284896823</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.012090468176304693</v>
       </c>
       <c r="B73">
-        <v>0.0011271571232864355</v>
+        <v>0.001378737745911742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.010747082823381951</v>
       </c>
       <c r="B74">
-        <v>0.00092957055421973337</v>
+        <v>0.0011740666884516727</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0094036974704592071</v>
       </c>
       <c r="B75">
-        <v>0.00072525634731022341</v>
+        <v>0.00096063261115781229</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0080603121175364632</v>
       </c>
       <c r="B76">
-        <v>0.00051942795978974945</v>
+        <v>0.00074296728251609394</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0067169267646137185</v>
       </c>
       <c r="B77">
-        <v>0.00031687927769774712</v>
+        <v>0.00052523335063138434</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0053735414116909755</v>
       </c>
       <c r="B78">
-        <v>0.00012054553388458637</v>
+        <v>0.00030996286864669326</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0040301560587682316</v>
       </c>
       <c r="B79">
-        <v>-6.43861036936964E-05</v>
+        <v>0.00010165632592755451</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0026867707058454877</v>
       </c>
       <c r="B80">
-        <v>-0.00022862315095404037</v>
+        <v>-9.1597844955920509E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0013433853529227439</v>
       </c>
       <c r="B81">
-        <v>-0.0003488896784766965</v>
+        <v>-0.00024947916236041351</v>
       </c>
     </row>
     <row r="82" spans="1:2">
